--- a/processo_2/synthetic_proposals/PROPOSTA_018/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_018/ficha_pontuacao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,12 +804,12 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6542-1798</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -821,124 +821,118 @@
           <t>Revista Científica Avançada 2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5105-1320</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Propriedade Intelectual</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Revista Científica Avançada 3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>9499-6493</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.1. Patente aceita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>sem teto</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+          <t>Propriedade Intelectual</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
+          <t>2.1. Patente aceita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>2.2. Patente depositada</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sem teto</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Livros e Capítulos</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3.1. Livros publicados (com ISBN)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sem teto</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.2. Capítulos de livros publicados</t>
+          <t>3.1. Livros publicados (com ISBN)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -947,13 +941,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -961,7 +955,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.3. Tradução de livros completos</t>
+          <t>3.2. Capítulos de livros publicados</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -970,13 +964,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
@@ -984,22 +978,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3.4. Tradução de capítulos de livros</t>
+          <t>3.3. Tradução de livros completos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
@@ -1007,22 +1001,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3.5. Organização e editoração de livros</t>
+          <t>3.4. Tradução de capítulos de livros</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr"/>
     </row>
@@ -1030,7 +1024,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.6. Confecção de mapas, cartas geográficas e maquetes</t>
+          <t>3.5. Organização e editoração de livros</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1053,62 +1047,68 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
+          <t>3.6. Confecção de mapas, cartas geográficas e maquetes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>3.7. Assessoria/Consultoria científica/Parecer ad hoc</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sem teto</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>1</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Somatório 1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>31</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PARTE II – Experiência profissional a partir de janeiro de 2020...</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Orientações Concluídas</t>
+          <t>PARTE II – Experiência profissional a partir de janeiro de 2020...</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1118,45 +1118,39 @@
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.1. Trabalho de conclusão de curso de graduação</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
+          <t>Orientações Concluídas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.2. Iniciação Científica (PIBIC/PIBITI etc)</t>
+          <t>4.1. Trabalho de conclusão de curso de graduação</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1167,22 +1161,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.3. Tutoria PET</t>
+          <t>4.2. Iniciação Científica (PIBIC/PIBITI etc)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="E36" t="n">
-        <v>20</v>
-      </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr"/>
     </row>
@@ -1190,19 +1184,19 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.4. Doutorado</t>
+          <t>4.3. Tutoria PET</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1213,22 +1207,22 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4.5. Mestrado</t>
+          <t>4.4. Doutorado</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr"/>
     </row>
@@ -1236,19 +1230,19 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.6. Especialização</t>
+          <t>4.5. Mestrado</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1259,22 +1253,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4.7. Pós-Doutorado</t>
+          <t>4.6. Especialização</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1282,12 +1276,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4.8. Coorientação de Doutorado</t>
+          <t>4.7. Pós-Doutorado</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1305,19 +1299,19 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.9. Coorientação de Mestrado</t>
+          <t>4.8. Coorientação de Doutorado</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1328,12 +1322,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4.10. Tutor ou Preceptor de Residência</t>
+          <t>4.9. Coorientação de Mestrado</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1348,50 +1342,50 @@
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4.10. Tutor ou Preceptor de Residência</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Bancas Examinadoras</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>5.1. Qualificação de Doutorado</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4</v>
-      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5.2. Defesa de Tese de Doutorado</t>
+          <t>5.1. Qualificação de Doutorado</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1403,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1414,7 +1408,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5.3. Qualificação de Mestrado</t>
+          <t>5.2. Defesa de Tese de Doutorado</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1426,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1437,7 +1431,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.4. Defesa de Dissertação de Mestrado</t>
+          <t>5.3. Qualificação de Mestrado</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1449,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1460,7 +1454,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.5. Avaliação de TFC (lato sensu)</t>
+          <t>5.4. Defesa de Dissertação de Mestrado</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1472,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1483,7 +1477,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5.6. Concurso Público, avaliação de IES ou PIBIC</t>
+          <t>5.5. Avaliação de TFC (lato sensu)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1495,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1506,7 +1500,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5.7. Professor Titular</t>
+          <t>5.6. Concurso Público, avaliação de IES ou PIBIC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1526,62 +1520,62 @@
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5.7. Professor Titular</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Atuação Institucional</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>6.1. Professor Permanente (por programa)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>5</v>
-      </c>
-      <c r="F53" t="n">
-        <v>10</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6.2. Professor Colaborador (por programa)</t>
+          <t>6.1. Professor Permanente (por programa)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1592,19 +1586,19 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6.3. Professor com bolsa de produtividade - CNPq</t>
+          <t>6.2. Professor Colaborador (por programa)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1615,19 +1609,19 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6.4. Coordenador de projeto com fomento</t>
+          <t>6.3. Professor com bolsa de produtividade - CNPq</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1638,62 +1632,68 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
+          <t>6.4. Coordenador de projeto com fomento</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>6.5. Líder de grupo de pesquisa</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sem teto</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Somatório 2</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>61</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>PARTE III – Produção artística e cultural e organização de eventos</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>10</v>
+      </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Produção artística e cultural e organização de eventos</t>
+          <t>PARTE III – Produção artística e cultural e organização de eventos</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1703,33 +1703,27 @@
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.1. Apresentação de Obra Artística</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>sem teto</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
+          <t>Produção artística e cultural e organização de eventos</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.2. Criação de Obra Artística</t>
+          <t>7.1. Apresentação de Obra Artística</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1752,12 +1746,12 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7.3. Produção de Evento Cultural/Artístico</t>
+          <t>7.2. Criação de Obra Artística</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1775,7 +1769,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.4. Coordenador de evento internacional cadastrado na UFMS</t>
+          <t>7.3. Produção de Evento Cultural/Artístico</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1784,13 +1778,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1798,7 +1792,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7.5. Coordenador de evento nacional cadastrado na UFMS</t>
+          <t>7.4. Coordenador de evento internacional cadastrado na UFMS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1810,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1821,44 +1815,52 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
+          <t>7.5. Coordenador de evento nacional cadastrado na UFMS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>7.6. Coordenador de evento local cadastrado na UFMS</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
         <v>1</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Somatório 3</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TOTAL DA PONTUAÇÃO (Somatório 1 + 2 + 3)</t>
+          <t>Somatório 3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1866,9 +1868,24 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TOTAL DA PONTUAÇÃO (Somatório 1 + 2 + 3)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>30</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
